--- a/verification/report-samples/trips-full-field.xlsx
+++ b/verification/report-samples/trips-full-field.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Full-field register" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$X5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$AD7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Full-field register'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -23,76 +23,94 @@
     <t>Selected period 2026-01-01 to 2026-12-31; current master records; loans cumulative through cutoff including opening principal.</t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>vehical</t>
-  </si>
-  <si>
-    <t>driver</t>
-  </si>
-  <si>
-    <t>cycle no</t>
-  </si>
-  <si>
-    <t>fair</t>
-  </si>
-  <si>
-    <t>desel</t>
-  </si>
-  <si>
-    <t>tool</t>
-  </si>
-  <si>
-    <t>pp</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>inam</t>
-  </si>
-  <si>
-    <t>servise</t>
-  </si>
-  <si>
-    <t>parking</t>
-  </si>
-  <si>
-    <t>mobil oil</t>
-  </si>
-  <si>
-    <t>other expense</t>
-  </si>
-  <si>
-    <t>driver cycle com</t>
-  </si>
-  <si>
-    <t>total expense</t>
-  </si>
-  <si>
-    <t>profit</t>
-  </si>
-  <si>
-    <t>start km</t>
-  </si>
-  <si>
-    <t>end km</t>
-  </si>
-  <si>
-    <t>total km</t>
-  </si>
-  <si>
-    <t>liter</t>
-  </si>
-  <si>
-    <t>average</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>remarks</t>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Cycle number</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Route notes</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>Fuel measurement basis</t>
+  </si>
+  <si>
+    <t>Weight unit</t>
+  </si>
+  <si>
+    <t>Fare (PKR)</t>
+  </si>
+  <si>
+    <t>Diesel (PKR)</t>
+  </si>
+  <si>
+    <t>Tolls (PKR)</t>
+  </si>
+  <si>
+    <t>Punjab Police (PKR)</t>
+  </si>
+  <si>
+    <t>Food (PKR)</t>
+  </si>
+  <si>
+    <t>Inam / reward (PKR)</t>
+  </si>
+  <si>
+    <t>Service (PKR)</t>
+  </si>
+  <si>
+    <t>Parking (PKR)</t>
+  </si>
+  <si>
+    <t>Engine oil (PKR)</t>
+  </si>
+  <si>
+    <t>Other expenses (PKR)</t>
+  </si>
+  <si>
+    <t>Driver cycle commission (PKR)</t>
+  </si>
+  <si>
+    <t>Total expenses (PKR)</t>
+  </si>
+  <si>
+    <t>Profit (PKR)</t>
+  </si>
+  <si>
+    <t>Start odometer (km)</t>
+  </si>
+  <si>
+    <t>End odometer (km)</t>
+  </si>
+  <si>
+    <t>Total distance (km)</t>
+  </si>
+  <si>
+    <t>Fuel (litres)</t>
+  </si>
+  <si>
+    <t>Average (km/L)</t>
+  </si>
+  <si>
+    <t>Cargo weight</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
   <si>
     <t>TEST-001</t>
@@ -104,7 +122,25 @@
     <t>TEST-CYCLE-001</t>
   </si>
   <si>
+    <t>TEST Depot A</t>
+  </si>
+  <si>
+    <t>TEST Depot B</t>
+  </si>
+  <si>
+    <t>TEST Depot A / TEST Depot B</t>
+  </si>
+  <si>
+    <t>measured</t>
+  </si>
+  <si>
+    <t>metric tonnes</t>
+  </si>
+  <si>
     <t>TEST trip remarks</t>
+  </si>
+  <si>
+    <t>Signature: __________________________</t>
   </si>
 </sst>
 </file>
@@ -229,7 +265,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -594,29 +630,38 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="2" max="4" width="22" style="2" customWidth="1"/>
-    <col min="5" max="17" width="22" style="3" customWidth="1"/>
-    <col min="18" max="23" width="22" style="4" customWidth="1"/>
-    <col min="24" max="24" width="22" style="2" customWidth="1"/>
+    <col min="2" max="8" width="22" style="2" customWidth="1"/>
+    <col min="9" max="9" width="30" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22" style="2" customWidth="1"/>
+    <col min="11" max="13" width="22" style="3" customWidth="1"/>
+    <col min="14" max="14" width="30" style="3" customWidth="1"/>
+    <col min="15" max="15" width="22" style="3" customWidth="1"/>
+    <col min="16" max="16" width="30" style="3" customWidth="1"/>
+    <col min="17" max="19" width="22" style="3" customWidth="1"/>
+    <col min="20" max="22" width="30" style="3" customWidth="1"/>
+    <col min="23" max="23" width="22" style="3" customWidth="1"/>
+    <col min="24" max="26" width="30" style="4" customWidth="1"/>
+    <col min="27" max="29" width="22" style="4" customWidth="1"/>
+    <col min="30" max="30" width="22" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
@@ -624,27 +669,33 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="7"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="7"/>
     </row>
-    <row r="2" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
       <c r="M2" s="13"/>
@@ -652,15 +703,21 @@
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="12"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="12"/>
     </row>
-    <row r="4" ht="40" customHeight="1" spans="1:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="40" customHeight="1" spans="1:30" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -673,22 +730,22 @@
       <c r="D4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="17" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="18" t="s">
@@ -712,104 +769,172 @@
       <c r="Q4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="R4" s="19" t="s">
+      <c r="R4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="S4" s="19" t="s">
+      <c r="S4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="19" t="s">
+      <c r="T4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="19" t="s">
+      <c r="U4" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="19" t="s">
+      <c r="V4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="W4" s="19" t="s">
+      <c r="W4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="X4" s="17" t="s">
+      <c r="X4" s="19" t="s">
         <v>25</v>
       </c>
+      <c r="Y4" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="13">
+        <v>34</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="13">
         <v>80000</v>
       </c>
-      <c r="F5" s="13">
+      <c r="L5" s="13">
         <v>29000</v>
       </c>
-      <c r="G5" s="13">
+      <c r="M5" s="13">
         <v>3000</v>
       </c>
-      <c r="H5" s="13">
+      <c r="N5" s="13">
         <v>0</v>
       </c>
-      <c r="I5" s="13">
+      <c r="O5" s="13">
         <v>1200</v>
       </c>
-      <c r="J5" s="13">
+      <c r="P5" s="13">
         <v>0</v>
       </c>
-      <c r="K5" s="13">
+      <c r="Q5" s="13">
         <v>0</v>
       </c>
-      <c r="L5" s="13">
+      <c r="R5" s="13">
         <v>0</v>
       </c>
-      <c r="M5" s="13">
+      <c r="S5" s="13">
         <v>0</v>
       </c>
-      <c r="N5" s="13">
+      <c r="T5" s="13">
         <v>800</v>
       </c>
-      <c r="O5" s="13">
+      <c r="U5" s="13">
         <v>2000</v>
       </c>
-      <c r="P5" s="13">
+      <c r="V5" s="13">
         <v>36000</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="W5" s="13">
         <v>44000</v>
       </c>
-      <c r="R5" s="14">
+      <c r="X5" s="14">
         <v>144844</v>
       </c>
-      <c r="S5" s="14">
+      <c r="Y5" s="14">
         <v>145382</v>
       </c>
-      <c r="T5" s="14">
+      <c r="Z5" s="14">
         <v>538</v>
       </c>
-      <c r="U5" s="14">
+      <c r="AA5" s="14">
         <v>68</v>
       </c>
-      <c r="V5" s="14">
+      <c r="AB5" s="14">
         <v>7.91</v>
       </c>
-      <c r="W5" s="14">
+      <c r="AC5" s="14">
         <v>12.345</v>
       </c>
-      <c r="X5" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="AD5" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:X4"/>
+  <autoFilter ref="A4:AD4"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
